--- a/tests/samples/multi_sheet.xlsx
+++ b/tests/samples/multi_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\contacts manager\tests\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D85E236-7990-4DE5-B6A2-3BC8B098E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F26E6E1-4EB6-4CEF-9B41-6C7523B0C05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{F620E3E3-C751-4204-B12D-218A8EBC8D6F}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{5A36C8BF-D224-4E43-9C26-D460FD0BE329}"/>
   </bookViews>
   <sheets>
     <sheet name="تعليمات" sheetId="3" r:id="rId1"/>
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7750A0-0E52-4382-B9D9-B725B0D02CC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0629BF40-B2D8-41BD-933D-B17E5D6FC8FE}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -464,7 +464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D04F5D-92C1-4BBB-A302-D9369D475965}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF91D4C-C5AC-46B0-B69D-D3752205845B}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -545,7 +545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893B91B5-F678-45AD-82EB-585F8CB02AE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE4D870-FF8C-45B0-ABC6-5E7E0AA28050}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
